--- a/xls/SimulacaoTesteKS.xlsx
+++ b/xls/SimulacaoTesteKS.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2024\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_1826629AE1EDDF2570BD6844089338617B5A5C59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05D3E418-B3A1-4C76-8471-249DCA71560D}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="5370" windowWidth="20730" windowHeight="5280"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exemplo 3" sheetId="20" r:id="rId1"/>
     <sheet name="Monte Carlo" sheetId="19" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -44,9 +58,6 @@
   </si>
   <si>
     <t>FRA</t>
-  </si>
-  <si>
-    <t>#http://www.dpi.inpe.br/~camilo/estatistica</t>
   </si>
   <si>
     <r>
@@ -231,19 +242,22 @@
     <t>Valor-P =</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER202, INPE, 2024</t>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
+  </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -330,13 +344,6 @@
       <family val="4"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Comic Sans MS"/>
@@ -404,7 +411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -416,7 +423,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -425,44 +432,41 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -495,9 +499,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -535,9 +539,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -572,7 +576,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -607,7 +611,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -780,213 +784,210 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15" style="10" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="10"/>
-    <col min="6" max="7" width="8.42578125" style="10" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="10"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" customWidth="1"/>
+    <col min="6" max="7" width="8.42578125" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" style="5" customWidth="1"/>
     <col min="11" max="12" width="11.42578125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15" style="10" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="10"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="13" t="s">
+      <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>12</v>
       </c>
       <c r="K4" s="5">
         <f>COUNT(B5:B19)</f>
         <v>15</v>
       </c>
       <c r="L4" s="5"/>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="13" t="s">
+      <c r="O4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="R4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="T4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="V4" s="15"/>
+      <c r="V4" s="13"/>
       <c r="W4" s="5"/>
     </row>
-    <row r="5" spans="1:29" s="11" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" s="9" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4">
         <v>81</v>
       </c>
       <c r="C5" s="4">
         <v>56</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="11">
         <v>54</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="14">
         <f t="shared" ref="F5:F27" si="0">COUNTIF(B$5:B$19,CONCATENATE("&lt;=",E5))/$K$4</f>
         <v>0</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="14">
         <f t="shared" ref="G5:G27" si="1">COUNTIF(C$5:C$19,CONCATENATE("&lt;=",E5))/$K$4</f>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="14">
         <f>ABS(F5-G5)</f>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="N5" s="4">
         <f t="shared" ref="N5:N19" ca="1" si="2">U30</f>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" ref="O5:O19" ca="1" si="3">U45</f>
-        <v>80</v>
-      </c>
-      <c r="Q5" s="13">
+        <v>88</v>
+      </c>
+      <c r="Q5" s="11">
         <v>54</v>
       </c>
-      <c r="R5" s="16">
+      <c r="R5" s="14">
         <f t="shared" ref="R5:R27" ca="1" si="4">COUNTIF(N$5:N$19,CONCATENATE("&lt;=",Q5))/$K$4</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="S5" s="14">
+        <f t="shared" ref="S5:S27" ca="1" si="5">COUNTIF(O$5:O$19,CONCATENATE("&lt;=",Q5))/$K$4</f>
         <v>0</v>
       </c>
-      <c r="S5" s="16">
-        <f t="shared" ref="S5:S27" ca="1" si="5">COUNTIF(O$5:O$19,CONCATENATE("&lt;=",Q5))/$K$4</f>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="T5" s="16">
+      <c r="T5" s="14">
         <f ca="1">ABS(R5-S5)</f>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="AC5" s="10"/>
-    </row>
-    <row r="6" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC5"/>
+    </row>
+    <row r="6" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4">
         <v>78</v>
       </c>
       <c r="C6" s="4">
         <v>55</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <v>55</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="14">
         <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="14">
         <f t="shared" ref="H6:H27" si="6">ABS(F6-G6)</f>
         <v>0.2</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="15">
         <f>MAX(H5:H27)</f>
         <v>0.26666666666666661</v>
       </c>
-      <c r="L6" s="17"/>
+      <c r="L6" s="15"/>
       <c r="N6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O6" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>58</v>
-      </c>
-      <c r="Q6" s="13">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="11">
         <v>55</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="S6" s="16">
+      <c r="S6" s="14">
         <f t="shared" ca="1" si="5"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="T6" s="16">
+      <c r="T6" s="14">
         <f t="shared" ref="T6:T27" ca="1" si="7">ABS(R6-S6)</f>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="W6" s="17">
+      <c r="W6" s="15">
         <f ca="1">MAX(T5:T27)</f>
-        <v>0.39999999999999997</v>
-      </c>
-      <c r="AC6" s="10"/>
-    </row>
-    <row r="7" spans="1:29" s="11" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.2</v>
+      </c>
+      <c r="AC6"/>
+    </row>
+    <row r="7" spans="1:29" s="9" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4">
         <v>61</v>
       </c>
       <c r="C7" s="4">
         <v>76</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11">
         <v>56</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="14">
         <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="14">
         <f t="shared" si="1"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="14">
         <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
@@ -1000,55 +1001,55 @@
       <c r="L7" s="5"/>
       <c r="N7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O7" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>61</v>
-      </c>
-      <c r="Q7" s="13">
+        <v>91</v>
+      </c>
+      <c r="Q7" s="11">
         <v>56</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="14">
         <f t="shared" ca="1" si="4"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="S7" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="S7" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="T7" s="16">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="T7" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>0.2</v>
+        <v>6.666666666666668E-2</v>
       </c>
       <c r="V7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="W7" s="18">
+      <c r="W7" s="16">
         <f ca="1">W6*$K$4</f>
-        <v>5.9999999999999991</v>
-      </c>
-      <c r="AC7" s="10"/>
-    </row>
-    <row r="8" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="AC7"/>
+    </row>
+    <row r="8" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="4">
         <v>89</v>
       </c>
       <c r="C8" s="4">
         <v>54</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <v>58</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="14">
         <f t="shared" si="0"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="14">
         <f t="shared" si="1"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="14">
         <f t="shared" si="6"/>
         <v>0.13333333333333333</v>
       </c>
@@ -1057,55 +1058,55 @@
       <c r="L8" s="5"/>
       <c r="N8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="O8" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>83</v>
-      </c>
-      <c r="Q8" s="13">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="11">
         <v>58</v>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="14">
         <f t="shared" ca="1" si="4"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="S8" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="S8" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="T8" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="T8" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>0.13333333333333333</v>
+        <v>0</v>
       </c>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
-      <c r="AC8" s="10"/>
-    </row>
-    <row r="9" spans="1:29" s="11" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="AC8"/>
+    </row>
+    <row r="9" spans="1:29" s="9" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="4">
         <v>69</v>
       </c>
       <c r="C9" s="4">
         <v>83</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11">
         <v>61</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="14">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="14">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="14">
         <f t="shared" si="6"/>
         <v>0.1333333333333333</v>
       </c>
-      <c r="J9" s="21" t="s">
-        <v>19</v>
+      <c r="J9" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="K9" s="8">
         <v>0.05</v>
@@ -1113,257 +1114,257 @@
       <c r="L9" s="8"/>
       <c r="N9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="O9" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>81</v>
-      </c>
-      <c r="Q9" s="13">
+        <v>64</v>
+      </c>
+      <c r="Q9" s="11">
         <v>61</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="S9" s="16">
+      <c r="S9" s="14">
         <f t="shared" ca="1" si="5"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="T9" s="16">
+      <c r="T9" s="14">
         <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
-      <c r="AC9" s="10"/>
-    </row>
-    <row r="10" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC9"/>
+    </row>
+    <row r="10" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="4">
         <v>58</v>
       </c>
       <c r="C10" s="4">
         <v>97</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <v>64</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="14">
         <f t="shared" si="0"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="14">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="14">
         <f t="shared" si="6"/>
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="N10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="O10" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>89</v>
-      </c>
-      <c r="Q10" s="13">
+        <v>95</v>
+      </c>
+      <c r="Q10" s="11">
         <v>64</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="14">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="S10" s="14">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="T10" s="14">
+        <f t="shared" ca="1" si="7"/>
+        <v>6.6666666666666652E-2</v>
+      </c>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="AC10"/>
+    </row>
+    <row r="11" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="4">
+        <v>64</v>
+      </c>
+      <c r="C11" s="4">
+        <v>85</v>
+      </c>
+      <c r="E11" s="11">
+        <v>66</v>
+      </c>
+      <c r="F11" s="14">
+        <f t="shared" si="0"/>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="G11" s="14">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+      <c r="H11" s="14">
+        <f t="shared" si="6"/>
+        <v>0.13333333333333336</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="O11" s="4">
+        <f t="shared" ca="1" si="3"/>
+        <v>58</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>66</v>
+      </c>
+      <c r="R11" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="S10" s="16">
+      <c r="S11" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="T10" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="T11" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>6.6666666666666652E-2</v>
-      </c>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="AC10" s="10"/>
-    </row>
-    <row r="11" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="4">
-        <v>64</v>
-      </c>
-      <c r="C11" s="4">
-        <v>85</v>
-      </c>
-      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="AC11"/>
+    </row>
+    <row r="12" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="4">
+        <v>84</v>
+      </c>
+      <c r="C12" s="4">
         <v>66</v>
       </c>
-      <c r="F11" s="16">
+      <c r="E12" s="11">
+        <v>69</v>
+      </c>
+      <c r="F12" s="14">
         <f t="shared" si="0"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="G11" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G12" s="14">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="H11" s="16">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="H12" s="14">
         <f t="shared" si="6"/>
         <v>0.13333333333333336</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>91</v>
-      </c>
-      <c r="O11" s="4">
+        <v>84</v>
+      </c>
+      <c r="O12" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>87</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>66</v>
-      </c>
-      <c r="R11" s="16">
+        <v>83</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>69</v>
+      </c>
+      <c r="R12" s="14">
         <f t="shared" ca="1" si="4"/>
-        <v>0.4</v>
-      </c>
-      <c r="S11" s="16">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="S12" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="T11" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="T12" s="14">
         <f t="shared" ca="1" si="7"/>
         <v>0.13333333333333336</v>
       </c>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="AC11" s="10"/>
-    </row>
-    <row r="12" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="4">
-        <v>84</v>
-      </c>
-      <c r="C12" s="4">
-        <v>66</v>
-      </c>
-      <c r="E12" s="13">
-        <v>69</v>
-      </c>
-      <c r="F12" s="16">
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="AC12"/>
+    </row>
+    <row r="13" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="4">
+        <v>89</v>
+      </c>
+      <c r="C13" s="4">
+        <v>78</v>
+      </c>
+      <c r="E13" s="11">
+        <v>71</v>
+      </c>
+      <c r="F13" s="14">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G13" s="14">
         <f t="shared" si="1"/>
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="H12" s="16">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="H13" s="14">
         <f t="shared" si="6"/>
-        <v>0.13333333333333336</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N13" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>75</v>
-      </c>
-      <c r="O12" s="4">
+        <v>55</v>
+      </c>
+      <c r="O13" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>85</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>69</v>
-      </c>
-      <c r="R12" s="16">
+        <v>80</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>71</v>
+      </c>
+      <c r="R13" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.53333333333333333</v>
       </c>
-      <c r="S12" s="16">
+      <c r="S13" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="T12" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="T13" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="AC12" s="10"/>
-    </row>
-    <row r="13" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="4">
-        <v>89</v>
-      </c>
-      <c r="C13" s="4">
-        <v>78</v>
-      </c>
-      <c r="E13" s="13">
-        <v>71</v>
-      </c>
-      <c r="F13" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="AC13"/>
+    </row>
+    <row r="14" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="4">
+        <v>83</v>
+      </c>
+      <c r="C14" s="4">
+        <v>80</v>
+      </c>
+      <c r="E14" s="11">
+        <v>75</v>
+      </c>
+      <c r="F14" s="14">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G13" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="G14" s="14">
         <f t="shared" si="1"/>
         <v>0.53333333333333333</v>
       </c>
-      <c r="H13" s="16">
-        <f t="shared" si="6"/>
-        <v>0.2</v>
-      </c>
-      <c r="N13" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="O13" s="4">
-        <f t="shared" ca="1" si="3"/>
-        <v>83</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>71</v>
-      </c>
-      <c r="R13" s="16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.6</v>
-      </c>
-      <c r="S13" s="16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="T13" s="16">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="AC13" s="10"/>
-    </row>
-    <row r="14" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="4">
-        <v>83</v>
-      </c>
-      <c r="C14" s="4">
-        <v>80</v>
-      </c>
-      <c r="E14" s="13">
-        <v>75</v>
-      </c>
-      <c r="F14" s="16">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="G14" s="16">
-        <f t="shared" si="1"/>
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="H14" s="16">
+      <c r="H14" s="14">
         <f t="shared" si="6"/>
         <v>0.1333333333333333</v>
       </c>
-      <c r="J14" s="15" t="s">
-        <v>23</v>
+      <c r="J14" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="K14" s="5">
         <f t="array" ref="K14">CHOOSE(SUM(IF(O22:O33&gt;=K9,1,0))+1,0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15)</f>
@@ -1371,160 +1372,160 @@
       </c>
       <c r="N14" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O14" s="4">
         <f t="shared" ca="1" si="3"/>
+        <v>87</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>75</v>
+      </c>
+      <c r="R14" s="14">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="S14" s="14">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="T14" s="14">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="AC14" s="2"/>
+    </row>
+    <row r="15" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="4">
+        <v>88</v>
+      </c>
+      <c r="C15" s="4">
+        <v>61</v>
+      </c>
+      <c r="E15" s="11">
+        <v>76</v>
+      </c>
+      <c r="F15" s="14">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="G15" s="14">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
+      </c>
+      <c r="H15" s="14">
+        <f t="shared" si="6"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="21">
+        <f>COUNTIF('Monte Carlo'!B:B,CONCATENATE("&lt;=",K7))/COUNT('Monte Carlo'!B:B)</f>
+        <v>0.64319999999999999</v>
+      </c>
+      <c r="N15" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="O15" s="4">
+        <f t="shared" ca="1" si="3"/>
+        <v>83</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>76</v>
+      </c>
+      <c r="R15" s="14">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="S15" s="14">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="T15" s="14">
+        <f t="shared" ca="1" si="7"/>
+        <v>6.6666666666666652E-2</v>
+      </c>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="AC15"/>
+    </row>
+    <row r="16" spans="1:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="4">
+        <v>56</v>
+      </c>
+      <c r="C16" s="4">
+        <v>69</v>
+      </c>
+      <c r="E16" s="11">
         <v>78</v>
       </c>
-      <c r="Q14" s="13">
-        <v>75</v>
-      </c>
-      <c r="R14" s="16">
+      <c r="F16" s="14">
+        <f t="shared" si="0"/>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="G16" s="14">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H16" s="14">
+        <f t="shared" si="6"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="N16" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="O16" s="4">
+        <f t="shared" ca="1" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>78</v>
+      </c>
+      <c r="R16" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="S14" s="16">
+      <c r="S16" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="T14" s="16">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="T16" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>0.39999999999999997</v>
-      </c>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="AC14" s="20"/>
-    </row>
-    <row r="15" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="4">
-        <v>88</v>
-      </c>
-      <c r="C15" s="4">
-        <v>61</v>
-      </c>
-      <c r="E15" s="13">
-        <v>76</v>
-      </c>
-      <c r="F15" s="16">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="G15" s="16">
-        <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="H15" s="16">
-        <f t="shared" si="6"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="J15" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" s="24">
-        <f>COUNTIF('Monte Carlo'!B:B,CONCATENATE("&lt;=",K7))/COUNT('Monte Carlo'!B:B)</f>
-        <v>0.64319999999999999</v>
-      </c>
-      <c r="N15" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>55</v>
-      </c>
-      <c r="O15" s="4">
-        <f t="shared" ca="1" si="3"/>
-        <v>76</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>76</v>
-      </c>
-      <c r="R15" s="16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="S15" s="16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="T15" s="16">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="AC15" s="10"/>
-    </row>
-    <row r="16" spans="1:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="4">
-        <v>56</v>
-      </c>
-      <c r="C16" s="4">
-        <v>69</v>
-      </c>
-      <c r="E16" s="13">
-        <v>78</v>
-      </c>
-      <c r="F16" s="16">
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="AC16"/>
+    </row>
+    <row r="17" spans="2:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="4">
+        <v>87</v>
+      </c>
+      <c r="C17" s="4">
+        <v>71</v>
+      </c>
+      <c r="E17" s="11">
+        <v>80</v>
+      </c>
+      <c r="F17" s="14">
         <f t="shared" si="0"/>
         <v>0.46666666666666667</v>
       </c>
-      <c r="G16" s="16">
-        <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="H16" s="16">
-        <f t="shared" si="6"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="N16" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>69</v>
-      </c>
-      <c r="O16" s="4">
-        <f t="shared" ca="1" si="3"/>
-        <v>54</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>78</v>
-      </c>
-      <c r="R16" s="16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.73333333333333328</v>
-      </c>
-      <c r="S16" s="16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.4</v>
-      </c>
-      <c r="T16" s="16">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.33333333333333326</v>
-      </c>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="AC16" s="10"/>
-    </row>
-    <row r="17" spans="2:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="4">
-        <v>87</v>
-      </c>
-      <c r="C17" s="4">
-        <v>71</v>
-      </c>
-      <c r="E17" s="13">
-        <v>80</v>
-      </c>
-      <c r="F17" s="16">
-        <f t="shared" si="0"/>
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="G17" s="16">
+      <c r="G17" s="14">
         <f t="shared" si="1"/>
         <v>0.73333333333333328</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="14">
         <f t="shared" si="6"/>
         <v>0.26666666666666661</v>
       </c>
-      <c r="J17" s="15" t="s">
-        <v>22</v>
+      <c r="J17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="K17" s="5" t="str">
         <f>IF(K7&gt;=K14,"rejeito H0","aceito H0")</f>
@@ -1532,467 +1533,467 @@
       </c>
       <c r="N17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O17" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>97</v>
-      </c>
-      <c r="Q17" s="13">
+        <v>85</v>
+      </c>
+      <c r="Q17" s="11">
         <v>80</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="14">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="S17" s="14">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="T17" s="14">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="AC17"/>
+    </row>
+    <row r="18" spans="2:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="4">
+        <v>95</v>
+      </c>
+      <c r="C18" s="4">
+        <v>55</v>
+      </c>
+      <c r="E18" s="11">
+        <v>81</v>
+      </c>
+      <c r="F18" s="14">
+        <f t="shared" si="0"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="G18" s="14">
+        <f t="shared" si="1"/>
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="H18" s="14">
+        <f t="shared" si="6"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="N18" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="O18" s="4">
+        <f t="shared" ca="1" si="3"/>
+        <v>55</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>81</v>
+      </c>
+      <c r="R18" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.73333333333333328</v>
       </c>
-      <c r="S17" s="16">
+      <c r="S18" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="T17" s="16">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="T18" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>0.26666666666666661</v>
-      </c>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="AC17" s="10"/>
-    </row>
-    <row r="18" spans="2:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="4">
-        <v>95</v>
-      </c>
-      <c r="C18" s="4">
-        <v>55</v>
-      </c>
-      <c r="E18" s="13">
-        <v>81</v>
-      </c>
-      <c r="F18" s="16">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+    </row>
+    <row r="19" spans="2:29" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="4">
+        <v>75</v>
+      </c>
+      <c r="C19" s="4">
+        <v>91</v>
+      </c>
+      <c r="E19" s="11">
+        <v>83</v>
+      </c>
+      <c r="F19" s="14">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="G18" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="G19" s="14">
         <f t="shared" si="1"/>
-        <v>0.73333333333333328</v>
-      </c>
-      <c r="H18" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="H19" s="14">
         <f t="shared" si="6"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="N18" s="4">
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="N19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>66</v>
-      </c>
-      <c r="O18" s="4">
+        <v>97</v>
+      </c>
+      <c r="O19" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>61</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>81</v>
-      </c>
-      <c r="R18" s="16">
+        <v>75</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>83</v>
+      </c>
+      <c r="R19" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.73333333333333328</v>
       </c>
-      <c r="S18" s="16">
+      <c r="S19" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="T18" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="T19" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-    </row>
-    <row r="19" spans="2:29" s="11" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="4">
-        <v>75</v>
-      </c>
-      <c r="C19" s="4">
-        <v>91</v>
-      </c>
-      <c r="E19" s="13">
-        <v>83</v>
-      </c>
-      <c r="F19" s="16">
+        <v>6.6666666666666652E-2</v>
+      </c>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+    </row>
+    <row r="20" spans="2:29" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="11">
+        <v>84</v>
+      </c>
+      <c r="F20" s="14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="G19" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G20" s="14">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H20" s="14">
+        <f t="shared" si="6"/>
+        <v>0.13333333333333341</v>
+      </c>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="Q20" s="11">
+        <v>84</v>
+      </c>
+      <c r="R20" s="14">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="S20" s="14">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="T20" s="14">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.13333333333333341</v>
+      </c>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="21" spans="2:29" s="2" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E21" s="11">
+        <v>85</v>
+      </c>
+      <c r="F21" s="14">
+        <f t="shared" si="0"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G21" s="14">
+        <f t="shared" si="1"/>
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H21" s="14">
         <f t="shared" si="6"/>
         <v>0.20000000000000007</v>
       </c>
-      <c r="N19" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>56</v>
-      </c>
-      <c r="O19" s="4">
-        <f t="shared" ca="1" si="3"/>
-        <v>88</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>83</v>
-      </c>
-      <c r="R19" s="16">
+      <c r="N21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>85</v>
+      </c>
+      <c r="R21" s="14">
         <f t="shared" ca="1" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="S21" s="14">
+        <f t="shared" ca="1" si="5"/>
         <v>0.73333333333333328</v>
       </c>
-      <c r="S19" s="16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="T19" s="16">
+      <c r="T21" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>6.6666666666666652E-2</v>
-      </c>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-    </row>
-    <row r="20" spans="2:29" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E20" s="13">
-        <v>84</v>
-      </c>
-      <c r="F20" s="16">
+        <v>6.6666666666666763E-2</v>
+      </c>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+    </row>
+    <row r="22" spans="2:29" s="2" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E22" s="11">
+        <v>87</v>
+      </c>
+      <c r="F22" s="14">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="G20" s="16">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="G22" s="14">
         <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="H20" s="16">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H22" s="14">
         <f t="shared" si="6"/>
         <v>0.13333333333333341</v>
       </c>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="Q20" s="13">
-        <v>84</v>
-      </c>
-      <c r="R20" s="16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.8</v>
-      </c>
-      <c r="S20" s="16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="T20" s="16">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.13333333333333341</v>
-      </c>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-    </row>
-    <row r="21" spans="2:29" s="20" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E21" s="13">
-        <v>85</v>
-      </c>
-      <c r="F21" s="16">
-        <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="G21" s="16">
-        <f t="shared" si="1"/>
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="H21" s="16">
-        <f t="shared" si="6"/>
-        <v>0.20000000000000007</v>
-      </c>
-      <c r="N21" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>85</v>
-      </c>
-      <c r="R21" s="16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.8</v>
-      </c>
-      <c r="S21" s="16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.73333333333333328</v>
-      </c>
-      <c r="T21" s="16">
-        <f t="shared" ca="1" si="7"/>
-        <v>6.6666666666666763E-2</v>
-      </c>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-    </row>
-    <row r="22" spans="2:29" s="20" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E22" s="13">
-        <v>87</v>
-      </c>
-      <c r="F22" s="16">
-        <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
-      </c>
-      <c r="G22" s="16">
-        <f t="shared" si="1"/>
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="H22" s="16">
-        <f t="shared" si="6"/>
-        <v>0.13333333333333341</v>
-      </c>
-      <c r="N22" s="19">
+      <c r="N22" s="17">
         <v>0</v>
       </c>
       <c r="O22" s="7">
         <f>COUNTIF('Monte Carlo'!B:B,CONCATENATE("&gt;=",N22))/10000</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="Q22" s="11">
         <v>87</v>
       </c>
-      <c r="R22" s="16">
+      <c r="R22" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="S22" s="16">
+      <c r="S22" s="14">
         <f t="shared" ca="1" si="5"/>
         <v>0.8</v>
       </c>
-      <c r="T22" s="16">
+      <c r="T22" s="14">
         <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="V22" s="5"/>
       <c r="W22" s="5"/>
     </row>
-    <row r="23" spans="2:29" s="20" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E23" s="13">
+    <row r="23" spans="2:29" s="2" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="11">
         <v>88</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="14">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="14">
         <f t="shared" si="1"/>
         <v>0.8666666666666667</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="14">
         <f t="shared" si="6"/>
         <v>6.6666666666666652E-2</v>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="17">
         <v>1</v>
       </c>
       <c r="O23" s="7">
         <f>COUNTIF('Monte Carlo'!B:B,CONCATENATE("&gt;=",N23))/10000</f>
         <v>1</v>
       </c>
-      <c r="Q23" s="13">
+      <c r="Q23" s="11">
         <v>88</v>
       </c>
-      <c r="R23" s="16">
+      <c r="R23" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="S23" s="16">
+      <c r="S23" s="14">
         <f t="shared" ca="1" si="5"/>
         <v>0.8666666666666667</v>
       </c>
-      <c r="T23" s="16">
+      <c r="T23" s="14">
         <f t="shared" ca="1" si="7"/>
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="V23" s="5"/>
       <c r="W23" s="5"/>
     </row>
-    <row r="24" spans="2:29" s="20" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E24" s="13">
+    <row r="24" spans="2:29" s="2" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E24" s="11">
         <v>89</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="14">
         <f t="shared" si="0"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="14">
         <f t="shared" si="1"/>
         <v>0.8666666666666667</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="14">
         <f t="shared" si="6"/>
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
-      <c r="N24" s="19">
+      <c r="N24" s="17">
         <v>2</v>
       </c>
       <c r="O24" s="7">
         <f>COUNTIF('Monte Carlo'!B:B,CONCATENATE("&gt;=",N24))/10000</f>
         <v>0.99880000000000002</v>
       </c>
-      <c r="Q24" s="13">
+      <c r="Q24" s="11">
         <v>89</v>
       </c>
-      <c r="R24" s="16">
+      <c r="R24" s="14">
         <f t="shared" ca="1" si="4"/>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="S24" s="14">
+        <f t="shared" ca="1" si="5"/>
         <v>0.8666666666666667</v>
       </c>
-      <c r="S24" s="16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.93333333333333335</v>
-      </c>
-      <c r="T24" s="16">
+      <c r="T24" s="14">
         <f t="shared" ca="1" si="7"/>
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
     </row>
-    <row r="25" spans="2:29" s="20" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E25" s="13">
+    <row r="25" spans="2:29" s="2" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="11">
         <v>91</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="14">
         <f t="shared" si="0"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="14">
         <f t="shared" si="1"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
-      <c r="N25" s="19">
+      <c r="N25" s="17">
         <v>3</v>
       </c>
       <c r="O25" s="7">
         <f>COUNTIF('Monte Carlo'!B:B,CONCATENATE("&gt;=",N25))/10000</f>
         <v>0.92310000000000003</v>
       </c>
-      <c r="Q25" s="13">
+      <c r="Q25" s="11">
         <v>91</v>
       </c>
-      <c r="R25" s="16">
+      <c r="R25" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="S25" s="16">
+      <c r="S25" s="14">
         <f t="shared" ca="1" si="5"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="T25" s="16">
+      <c r="T25" s="14">
         <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
     </row>
-    <row r="26" spans="2:29" s="20" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E26" s="13">
+    <row r="26" spans="2:29" s="2" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E26" s="11">
         <v>95</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="14">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="14">
         <f t="shared" si="1"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="14">
         <f t="shared" si="6"/>
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
-      <c r="N26" s="19">
+      <c r="N26" s="17">
         <v>4</v>
       </c>
       <c r="O26" s="7">
         <f>COUNTIF('Monte Carlo'!B:B,CONCATENATE("&gt;=",N26))/10000</f>
         <v>0.6159</v>
       </c>
-      <c r="Q26" s="13">
+      <c r="Q26" s="11">
         <v>95</v>
       </c>
-      <c r="R26" s="16">
+      <c r="R26" s="14">
         <f t="shared" ca="1" si="4"/>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="S26" s="14">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
-      <c r="S26" s="16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.93333333333333335</v>
-      </c>
-      <c r="T26" s="16">
+      <c r="T26" s="14">
         <f t="shared" ca="1" si="7"/>
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="V26" s="5"/>
       <c r="W26" s="5"/>
     </row>
-    <row r="27" spans="2:29" s="20" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E27" s="13">
+    <row r="27" spans="2:29" s="2" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E27" s="11">
         <v>97</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="14">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
-      <c r="N27" s="19">
+      <c r="N27" s="17">
         <v>5</v>
       </c>
       <c r="O27" s="7">
         <f>COUNTIF('Monte Carlo'!B:B,CONCATENATE("&gt;=",N27))/10000</f>
         <v>0.35680000000000001</v>
       </c>
-      <c r="Q27" s="13">
+      <c r="Q27" s="11">
         <v>97</v>
       </c>
-      <c r="R27" s="16">
+      <c r="R27" s="14">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="S27" s="16">
+      <c r="S27" s="14">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
-      <c r="T27" s="16">
+      <c r="T27" s="14">
         <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="V27" s="5"/>
       <c r="W27" s="5"/>
     </row>
-    <row r="28" spans="2:29" s="20" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:29" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
-      <c r="N28" s="19">
+      <c r="N28" s="17">
         <v>6</v>
       </c>
       <c r="O28" s="7">
@@ -2001,7 +2002,7 @@
       </c>
     </row>
     <row r="29" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="N29" s="19">
+      <c r="N29" s="17">
         <v>7</v>
       </c>
       <c r="O29" s="7">
@@ -2009,20 +2010,20 @@
         <v>6.8699999999999997E-2</v>
       </c>
       <c r="Q29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="30" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="N30" s="19">
+      <c r="N30" s="17">
         <v>8</v>
       </c>
       <c r="O30" s="7">
@@ -2031,26 +2032,26 @@
       </c>
       <c r="Q30" s="6">
         <f ca="1">RAND()</f>
-        <v>0.59113589796884347</v>
+        <v>0.10830046393646486</v>
       </c>
       <c r="R30" s="1">
         <f t="shared" ref="R30:R44" si="8">B5</f>
         <v>81</v>
       </c>
-      <c r="S30" s="10">
+      <c r="S30">
         <v>1</v>
       </c>
       <c r="T30" s="6">
         <f t="shared" ref="T30:T59" ca="1" si="9">SMALL(Q$30:Q$59,S30)</f>
-        <v>7.8397368182262506E-3</v>
+        <v>5.7263474332079123E-2</v>
       </c>
       <c r="U30" s="1">
         <f t="shared" ref="U30:U59" ca="1" si="10">VLOOKUP(T30,Q$30:R$59,2,0)</f>
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="N31" s="19">
+      <c r="N31" s="17">
         <v>9</v>
       </c>
       <c r="O31" s="7">
@@ -2059,26 +2060,26 @@
       </c>
       <c r="Q31" s="6">
         <f t="shared" ref="Q31:Q59" ca="1" si="11">RAND()</f>
-        <v>0.74454533474423934</v>
+        <v>0.34048540362501978</v>
       </c>
       <c r="R31" s="1">
         <f t="shared" si="8"/>
         <v>78</v>
       </c>
-      <c r="S31" s="10">
+      <c r="S31">
         <v>2</v>
       </c>
       <c r="T31" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>4.6175081279288821E-2</v>
+        <v>6.0025102809193376E-2</v>
       </c>
       <c r="U31" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="N32" s="19">
+      <c r="N32" s="17">
         <v>10</v>
       </c>
       <c r="O32" s="7">
@@ -2087,26 +2088,26 @@
       </c>
       <c r="Q32" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.56855711270142661</v>
+        <v>8.9352119950816711E-2</v>
       </c>
       <c r="R32" s="1">
         <f t="shared" si="8"/>
         <v>61</v>
       </c>
-      <c r="S32" s="10">
+      <c r="S32">
         <v>3</v>
       </c>
       <c r="T32" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.17388661038108333</v>
+        <v>7.9715839568093361E-2</v>
       </c>
       <c r="U32" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="14:21" x14ac:dyDescent="0.3">
-      <c r="N33" s="19">
+      <c r="N33" s="17">
         <v>11</v>
       </c>
       <c r="O33" s="7">
@@ -2115,26 +2116,26 @@
       </c>
       <c r="Q33" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.40231628153164456</v>
+        <v>0.15401299035155602</v>
       </c>
       <c r="R33" s="1">
         <f t="shared" si="8"/>
         <v>89</v>
       </c>
-      <c r="S33" s="10">
+      <c r="S33">
         <v>4</v>
       </c>
       <c r="T33" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.17768607284454929</v>
+        <v>8.9352119950816711E-2</v>
       </c>
       <c r="U33" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="14:21" x14ac:dyDescent="0.3">
-      <c r="N34" s="19">
+      <c r="N34" s="17">
         <v>12</v>
       </c>
       <c r="O34" s="7">
@@ -2143,26 +2144,26 @@
       </c>
       <c r="Q34" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.33909830232434079</v>
+        <v>5.7263474332079123E-2</v>
       </c>
       <c r="R34" s="1">
         <f t="shared" si="8"/>
         <v>69</v>
       </c>
-      <c r="S34" s="10">
+      <c r="S34">
         <v>5</v>
       </c>
       <c r="T34" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.19079847741490785</v>
+        <v>0.10830046393646486</v>
       </c>
       <c r="U34" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="14:21" x14ac:dyDescent="0.3">
-      <c r="N35" s="19">
+      <c r="N35" s="17">
         <v>13</v>
       </c>
       <c r="O35" s="7">
@@ -2171,26 +2172,26 @@
       </c>
       <c r="Q35" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.55049245413530334</v>
+        <v>0.66163312789193784</v>
       </c>
       <c r="R35" s="1">
         <f t="shared" si="8"/>
         <v>58</v>
       </c>
-      <c r="S35" s="10">
+      <c r="S35">
         <v>6</v>
       </c>
       <c r="T35" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.22356830992609189</v>
+        <v>0.1415406375071615</v>
       </c>
       <c r="U35" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="14:21" x14ac:dyDescent="0.3">
-      <c r="N36" s="19">
+      <c r="N36" s="17">
         <v>14</v>
       </c>
       <c r="O36" s="7">
@@ -2199,26 +2200,26 @@
       </c>
       <c r="Q36" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>7.8397368182262506E-3</v>
+        <v>0.54277159543236164</v>
       </c>
       <c r="R36" s="1">
         <f t="shared" si="8"/>
         <v>64</v>
       </c>
-      <c r="S36" s="10">
+      <c r="S36">
         <v>7</v>
       </c>
       <c r="T36" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.26310418386905399</v>
+        <v>0.14409051353570046</v>
       </c>
       <c r="U36" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>91</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="14:21" x14ac:dyDescent="0.3">
-      <c r="N37" s="19">
+      <c r="N37" s="17">
         <v>15</v>
       </c>
       <c r="O37" s="7">
@@ -2227,484 +2228,484 @@
       </c>
       <c r="Q37" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.2960215436503737</v>
+        <v>0.14701380547364828</v>
       </c>
       <c r="R37" s="1">
         <f t="shared" si="8"/>
         <v>84</v>
       </c>
-      <c r="S37" s="10">
+      <c r="S37">
         <v>8</v>
       </c>
       <c r="T37" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.29114758325963475</v>
+        <v>0.14701380547364828</v>
       </c>
       <c r="U37" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q38" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.59184360833523475</v>
+        <v>0.23372858796263007</v>
       </c>
       <c r="R38" s="1">
         <f t="shared" si="8"/>
         <v>89</v>
       </c>
-      <c r="S38" s="10">
+      <c r="S38">
         <v>9</v>
       </c>
       <c r="T38" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.29292125587657192</v>
+        <v>0.15323855753429094</v>
       </c>
       <c r="U38" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q39" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.58059264748396222</v>
+        <v>0.67844958269036459</v>
       </c>
       <c r="R39" s="1">
         <f t="shared" si="8"/>
         <v>83</v>
       </c>
-      <c r="S39" s="10">
+      <c r="S39">
         <v>10</v>
       </c>
       <c r="T39" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.2960215436503737</v>
+        <v>0.15401299035155602</v>
       </c>
       <c r="U39" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q40" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.97774911227018435</v>
+        <v>0.46868184956294812</v>
       </c>
       <c r="R40" s="1">
         <f t="shared" si="8"/>
         <v>88</v>
       </c>
-      <c r="S40" s="10">
+      <c r="S40">
         <v>11</v>
       </c>
       <c r="T40" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.33177192395809052</v>
+        <v>0.23372858796263007</v>
       </c>
       <c r="U40" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>55</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q41" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.53211675747386666</v>
+        <v>0.53471803611154378</v>
       </c>
       <c r="R41" s="1">
         <f t="shared" si="8"/>
         <v>56</v>
       </c>
-      <c r="S41" s="10">
+      <c r="S41">
         <v>12</v>
       </c>
       <c r="T41" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.33909830232434079</v>
+        <v>0.26427230901969478</v>
       </c>
       <c r="U41" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q42" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.62033068535464198</v>
+        <v>0.7559979659013043</v>
       </c>
       <c r="R42" s="1">
         <f t="shared" si="8"/>
         <v>87</v>
       </c>
-      <c r="S42" s="10">
+      <c r="S42">
         <v>13</v>
       </c>
       <c r="T42" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.40231628153164456</v>
+        <v>0.27540135979266023</v>
       </c>
       <c r="U42" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q43" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.22356830992609189</v>
+        <v>0.56938080142965952</v>
       </c>
       <c r="R43" s="1">
         <f t="shared" si="8"/>
         <v>95</v>
       </c>
-      <c r="S43" s="10">
+      <c r="S43">
         <v>14</v>
       </c>
       <c r="T43" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.43179580861132882</v>
+        <v>0.34048540362501978</v>
       </c>
       <c r="U43" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q44" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.29114758325963475</v>
+        <v>0.96291403364067363</v>
       </c>
       <c r="R44" s="1">
         <f t="shared" si="8"/>
         <v>75</v>
       </c>
-      <c r="S44" s="10">
+      <c r="S44">
         <v>15</v>
       </c>
       <c r="T44" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.53211675747386666</v>
+        <v>0.41528870042082922</v>
       </c>
       <c r="U44" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>56</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q45" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.17388661038108333</v>
+        <v>0.14409051353570046</v>
       </c>
       <c r="R45" s="1">
         <f t="shared" ref="R45:R59" si="12">C5</f>
         <v>56</v>
       </c>
-      <c r="S45" s="10">
+      <c r="S45">
         <v>16</v>
       </c>
       <c r="T45" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.53829847772240103</v>
+        <v>0.46868184956294812</v>
       </c>
       <c r="U45" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q46" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.33177192395809052</v>
+        <v>0.90329066928137092</v>
       </c>
       <c r="R46" s="1">
         <f t="shared" si="12"/>
         <v>55</v>
       </c>
-      <c r="S46" s="10">
+      <c r="S46">
         <v>17</v>
       </c>
       <c r="T46" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.55049245413530334</v>
+        <v>0.47610647228105885</v>
       </c>
       <c r="U46" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q47" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.79897030232252952</v>
+        <v>0.47610647228105885</v>
       </c>
       <c r="R47" s="1">
         <f t="shared" si="12"/>
         <v>76</v>
       </c>
-      <c r="S47" s="10">
+      <c r="S47">
         <v>18</v>
       </c>
       <c r="T47" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.56855711270142661</v>
+        <v>0.51999330931911203</v>
       </c>
       <c r="U47" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>61</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="14:21" x14ac:dyDescent="0.3">
       <c r="Q48" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.86702083567870469</v>
+        <v>7.9715839568093361E-2</v>
       </c>
       <c r="R48" s="1">
         <f t="shared" si="12"/>
         <v>54</v>
       </c>
-      <c r="S48" s="10">
+      <c r="S48">
         <v>19</v>
       </c>
       <c r="T48" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.58059264748396222</v>
+        <v>0.53471803611154378</v>
       </c>
       <c r="U48" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>83</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q49" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.72211256638368326</v>
+        <v>0.75914588182306586</v>
       </c>
       <c r="R49" s="1">
         <f t="shared" si="12"/>
         <v>83</v>
       </c>
-      <c r="S49" s="10">
+      <c r="S49">
         <v>20</v>
       </c>
       <c r="T49" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.59113589796884347</v>
+        <v>0.54277159543236164</v>
       </c>
       <c r="U49" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q50" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.88217594307422897</v>
+        <v>0.41528870042082922</v>
       </c>
       <c r="R50" s="1">
         <f t="shared" si="12"/>
         <v>97</v>
       </c>
-      <c r="S50" s="10">
+      <c r="S50">
         <v>21</v>
       </c>
       <c r="T50" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.59184360833523475</v>
+        <v>0.56938080142965952</v>
       </c>
       <c r="U50" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q51" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.65060028483592758</v>
+        <v>0.82825045443035172</v>
       </c>
       <c r="R51" s="1">
         <f t="shared" si="12"/>
         <v>85</v>
       </c>
-      <c r="S51" s="10">
+      <c r="S51">
         <v>22</v>
       </c>
       <c r="T51" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.62033068535464198</v>
+        <v>0.66163312789193784</v>
       </c>
       <c r="U51" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q52" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.43179580861132882</v>
+        <v>0.26427230901969478</v>
       </c>
       <c r="R52" s="1">
         <f t="shared" si="12"/>
         <v>66</v>
       </c>
-      <c r="S52" s="10">
+      <c r="S52">
         <v>23</v>
       </c>
       <c r="T52" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.65060028483592758</v>
+        <v>0.67844958269036459</v>
       </c>
       <c r="U52" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q53" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.29292125587657192</v>
+        <v>6.0025102809193376E-2</v>
       </c>
       <c r="R53" s="1">
         <f t="shared" si="12"/>
         <v>78</v>
       </c>
-      <c r="S53" s="10">
+      <c r="S53">
         <v>24</v>
       </c>
       <c r="T53" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.72211256638368326</v>
+        <v>0.70266581466026434</v>
       </c>
       <c r="U53" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q54" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.53829847772240103</v>
+        <v>0.70266581466026434</v>
       </c>
       <c r="R54" s="1">
         <f t="shared" si="12"/>
         <v>80</v>
       </c>
-      <c r="S54" s="10">
+      <c r="S54">
         <v>25</v>
       </c>
       <c r="T54" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.74454533474423934</v>
+        <v>0.7559979659013043</v>
       </c>
       <c r="U54" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q55" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.93933326929927663</v>
+        <v>0.76178118369696612</v>
       </c>
       <c r="R55" s="1">
         <f t="shared" si="12"/>
         <v>61</v>
       </c>
-      <c r="S55" s="10">
+      <c r="S55">
         <v>26</v>
       </c>
       <c r="T55" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.79897030232252952</v>
+        <v>0.75914588182306586</v>
       </c>
       <c r="U55" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q56" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.17768607284454929</v>
+        <v>0.1415406375071615</v>
       </c>
       <c r="R56" s="1">
         <f t="shared" si="12"/>
         <v>69</v>
       </c>
-      <c r="S56" s="10">
+      <c r="S56">
         <v>27</v>
       </c>
       <c r="T56" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.86702083567870469</v>
+        <v>0.76178118369696612</v>
       </c>
       <c r="U56" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q57" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>4.6175081279288821E-2</v>
+        <v>0.27540135979266023</v>
       </c>
       <c r="R57" s="1">
         <f t="shared" si="12"/>
         <v>71</v>
       </c>
-      <c r="S57" s="10">
+      <c r="S57">
         <v>28</v>
       </c>
       <c r="T57" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.88217594307422897</v>
+        <v>0.82825045443035172</v>
       </c>
       <c r="U57" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q58" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.19079847741490785</v>
+        <v>0.15323855753429094</v>
       </c>
       <c r="R58" s="1">
         <f t="shared" si="12"/>
         <v>55</v>
       </c>
-      <c r="S58" s="10">
+      <c r="S58">
         <v>29</v>
       </c>
       <c r="T58" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.93933326929927663</v>
+        <v>0.90329066928137092</v>
       </c>
       <c r="U58" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q59" s="6">
         <f t="shared" ca="1" si="11"/>
-        <v>0.26310418386905399</v>
+        <v>0.51999330931911203</v>
       </c>
       <c r="R59" s="1">
         <f t="shared" si="12"/>
         <v>91</v>
       </c>
-      <c r="S59" s="10">
+      <c r="S59">
         <v>30</v>
       </c>
       <c r="T59" s="6">
         <f t="shared" ca="1" si="9"/>
-        <v>0.97774911227018435</v>
+        <v>0.96291403364067363</v>
       </c>
       <c r="U59" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2718,7 +2719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10001"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
